--- a/storage/Planilha_Controle_Despesas_v2601_1.xlsx
+++ b/storage/Planilha_Controle_Despesas_v2601_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\heleri\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{788AA648-65E4-4E4A-8475-4EB4A8DF74DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D56B1862-9836-4744-815E-597915F60698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2910" windowWidth="29040" windowHeight="15840" xr2:uid="{18AB48FE-6D0A-408B-81DD-88C3E4CE2477}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{18AB48FE-6D0A-408B-81DD-88C3E4CE2477}"/>
   </bookViews>
   <sheets>
     <sheet name="2601" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="49">
   <si>
     <t>ID</t>
   </si>
@@ -155,6 +155,27 @@
   </si>
   <si>
     <t>NF260219_Recibo_Arrumaí_Conserto_Porta_Terraço_Q260209_2225</t>
+  </si>
+  <si>
+    <t>Caiman Distribuidora</t>
+  </si>
+  <si>
+    <t>pagto reembolso</t>
+  </si>
+  <si>
+    <t>NF260218_Caiman_Distribuidora_Cera_Liquida_000.537.484</t>
+  </si>
+  <si>
+    <t>Cera Liquida Pretita 2L</t>
+  </si>
+  <si>
+    <t>Q260302_1955 Fechadura Porta Terraço Danificada</t>
+  </si>
+  <si>
+    <t>NF260225_Trava_Trinco_Para_Porta_Cadeado_90_Em_Aço_Inox_Fecho_Anti Roubo_Prateado</t>
+  </si>
+  <si>
+    <t>trava para porta aço inox fecho anti-roubo prateado</t>
   </si>
 </sst>
 </file>
@@ -246,7 +267,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -279,6 +300,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -607,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE75F61D-5328-424E-AC09-9079298705BC}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
@@ -624,31 +648,35 @@
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="10">
         <f>COUNTA(A3:A600)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D1" s="10" t="s">
         <v>37</v>
       </c>
       <c r="E1" s="8">
         <f>SUM(E3:E600)</f>
-        <v>851.30000000000007</v>
+        <v>914.08</v>
       </c>
       <c r="F1" s="5">
         <f>COUNTA(F3:F600)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G1" s="5">
         <f>COUNTA(G3:G600)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H1" s="5">
         <f>COUNTA(H3:H600)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I1" s="5">
         <f>COUNTIF(I3:I600,"sim")</f>
-        <v>6</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="14"/>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -904,6 +932,9 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="10">
+        <v>8</v>
+      </c>
       <c r="B10" s="10" t="s">
         <v>9</v>
       </c>
@@ -932,8 +963,75 @@
         <v>32</v>
       </c>
     </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="10">
+        <v>9</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="11">
+        <v>46071</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="1">
+        <v>28.02</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
+        <v>10</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="11">
+        <v>46078</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="1">
+        <v>34.76</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:I2" xr:uid="{CE75F61D-5328-424E-AC09-9079298705BC}"/>
+  <mergeCells count="1">
+    <mergeCell ref="J1:K1"/>
+  </mergeCells>
   <conditionalFormatting sqref="E1:E1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>

--- a/storage/Planilha_Controle_Despesas_v2601_1.xlsx
+++ b/storage/Planilha_Controle_Despesas_v2601_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\heleri\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D56B1862-9836-4744-815E-597915F60698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E8E48F-F84E-4689-A70C-F281E1E84248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{18AB48FE-6D0A-408B-81DD-88C3E4CE2477}"/>
+    <workbookView xWindow="-28920" yWindow="-2910" windowWidth="29040" windowHeight="15840" xr2:uid="{18AB48FE-6D0A-408B-81DD-88C3E4CE2477}"/>
   </bookViews>
   <sheets>
     <sheet name="2601" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="55">
   <si>
     <t>ID</t>
   </si>
@@ -176,6 +176,24 @@
   </si>
   <si>
     <t>trava para porta aço inox fecho anti-roubo prateado</t>
+  </si>
+  <si>
+    <t>Supermercado Mundial</t>
+  </si>
+  <si>
+    <t>NF260305_Material_Limpeza_Pedido_Zelador</t>
+  </si>
+  <si>
+    <t>2602_Atividades_Zeladoria_fev26_v1</t>
+  </si>
+  <si>
+    <t>(1) 1x DESINF. SANOL PINHO LAVANDA 2L — R$ 5,99 — R$ 5,99 ;(2) 1x DESINF. SANOL PINHO LAVANDA 2L — R$ 5,99 — R$ 5,99 ;(3) 1x LIMPA VIDROS LIMPOL 500ML — R$ 5,99 — R$ 5,99;(4) 1x LIMPA VIDROS LIMPOL 500ML — R$ 5,99 — R$ 5,99; (5) 1x L. ROUPAS PO SURF SEMI LAVANDA 800G — R$ 8,98 — R$ 8,98; (6) 1x LUVA LIMPANO MULTIUSO VISH G REF.35220 — R$ 9,35 — R$ 9,35</t>
+  </si>
+  <si>
+    <t>NF260309_Recibo_Arrumaí_Servico_Conserto_Porta_Alumínio</t>
+  </si>
+  <si>
+    <t>prestação de serviços de manutenção em porta de alumínio</t>
   </si>
 </sst>
 </file>
@@ -631,7 +649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE75F61D-5328-424E-AC09-9079298705BC}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
@@ -648,30 +666,30 @@
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="10">
         <f>COUNTA(A3:A600)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D1" s="10" t="s">
         <v>37</v>
       </c>
       <c r="E1" s="8">
         <f>SUM(E3:E600)</f>
-        <v>914.08</v>
+        <v>1007.87</v>
       </c>
       <c r="F1" s="5">
         <f>COUNTA(F3:F600)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G1" s="5">
         <f>COUNTA(G3:G600)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1" s="5">
         <f>COUNTA(H3:H600)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I1" s="5">
         <f>COUNTIF(I3:I600,"sim")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J1" s="14" t="s">
         <v>43</v>
@@ -1024,6 +1042,70 @@
         <v>12</v>
       </c>
       <c r="J12" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="10">
+        <v>11</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="11">
+        <v>46086</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="1">
+        <v>42.29</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="10">
+        <v>12</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="11">
+        <v>46084</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="1">
+        <v>51.5</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J14" s="4" t="s">
         <v>32</v>
       </c>
     </row>

--- a/storage/Planilha_Controle_Despesas_v2601_1.xlsx
+++ b/storage/Planilha_Controle_Despesas_v2601_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\heleri\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E8E48F-F84E-4689-A70C-F281E1E84248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432EC4D3-5DD5-45E0-BA0B-A48828241BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-2910" windowWidth="29040" windowHeight="15840" xr2:uid="{18AB48FE-6D0A-408B-81DD-88C3E4CE2477}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="59">
   <si>
     <t>ID</t>
   </si>
@@ -194,6 +194,18 @@
   </si>
   <si>
     <t>prestação de serviços de manutenção em porta de alumínio</t>
+  </si>
+  <si>
+    <t>Serralheria JBV</t>
+  </si>
+  <si>
+    <t>Q260316_1323 Janela do Terraço Com Avaria</t>
+  </si>
+  <si>
+    <t>NF260316_Massa_Vidro_Serralheria_JBV</t>
+  </si>
+  <si>
+    <t>1Kg Massa vidro</t>
   </si>
 </sst>
 </file>
@@ -649,7 +661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE75F61D-5328-424E-AC09-9079298705BC}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
@@ -666,30 +678,30 @@
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="10">
         <f>COUNTA(A3:A600)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="10" t="s">
         <v>37</v>
       </c>
       <c r="E1" s="8">
         <f>SUM(E3:E600)</f>
-        <v>1007.87</v>
+        <v>1017.87</v>
       </c>
       <c r="F1" s="5">
         <f>COUNTA(F3:F600)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G1" s="5">
         <f>COUNTA(G3:G600)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H1" s="5">
         <f>COUNTA(H3:H600)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I1" s="5">
         <f>COUNTIF(I3:I600,"sim")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J1" s="14" t="s">
         <v>43</v>
@@ -1106,6 +1118,38 @@
         <v>12</v>
       </c>
       <c r="J14" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="10">
+        <v>13</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="11">
+        <v>46092</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="1">
+        <v>10</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J15" s="4" t="s">
         <v>32</v>
       </c>
     </row>

--- a/storage/Planilha_Controle_Despesas_v2601_1.xlsx
+++ b/storage/Planilha_Controle_Despesas_v2601_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\heleri\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432EC4D3-5DD5-45E0-BA0B-A48828241BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522CD303-F346-40FA-993B-058D7A18487C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-2910" windowWidth="29040" windowHeight="15840" xr2:uid="{18AB48FE-6D0A-408B-81DD-88C3E4CE2477}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="62">
   <si>
     <t>ID</t>
   </si>
@@ -206,6 +206,15 @@
   </si>
   <si>
     <t>1Kg Massa vidro</t>
+  </si>
+  <si>
+    <t>Q260423_2044 Retirada Lixo Acumulado - Ausência Zelador Período 1 semana</t>
+  </si>
+  <si>
+    <t>NF260425_Serviço_Retirada_Lixo_Sr_Valdeci</t>
+  </si>
+  <si>
+    <t>serviço retirada lixo</t>
   </si>
 </sst>
 </file>
@@ -661,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE75F61D-5328-424E-AC09-9079298705BC}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
@@ -678,30 +687,30 @@
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="10">
         <f>COUNTA(A3:A600)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1" s="10" t="s">
         <v>37</v>
       </c>
       <c r="E1" s="8">
         <f>SUM(E3:E600)</f>
-        <v>1017.87</v>
+        <v>1067.8699999999999</v>
       </c>
       <c r="F1" s="5">
         <f>COUNTA(F3:F600)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G1" s="5">
         <f>COUNTA(G3:G600)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H1" s="5">
         <f>COUNTA(H3:H600)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I1" s="5">
         <f>COUNTIF(I3:I600,"sim")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J1" s="14" t="s">
         <v>43</v>
@@ -1150,6 +1159,38 @@
         <v>12</v>
       </c>
       <c r="J15" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="10">
+        <v>14</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="11">
+        <v>46137</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="13">
+        <v>50</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" s="4" t="s">
         <v>32</v>
       </c>
     </row>

--- a/storage/Planilha_Controle_Despesas_v2601_1.xlsx
+++ b/storage/Planilha_Controle_Despesas_v2601_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\heleri\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522CD303-F346-40FA-993B-058D7A18487C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD3A3EA-09FA-4358-B40D-BB18D0448151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2910" windowWidth="29040" windowHeight="15840" xr2:uid="{18AB48FE-6D0A-408B-81DD-88C3E4CE2477}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{18AB48FE-6D0A-408B-81DD-88C3E4CE2477}"/>
   </bookViews>
   <sheets>
     <sheet name="2601" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="66">
   <si>
     <t>ID</t>
   </si>
@@ -215,6 +215,18 @@
   </si>
   <si>
     <t>serviço retirada lixo</t>
+  </si>
+  <si>
+    <t>Assaí Mariz Barros</t>
+  </si>
+  <si>
+    <t>Q260512_0912 Iluminação - Troca Lâmpadas</t>
+  </si>
+  <si>
+    <t>NF260509_Lampadas_Troca_Q260512_0912</t>
+  </si>
+  <si>
+    <t>6xlampadas 50W + 1x lampada 12W</t>
   </si>
 </sst>
 </file>
@@ -670,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE75F61D-5328-424E-AC09-9079298705BC}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
@@ -687,30 +699,30 @@
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="10">
         <f>COUNTA(A3:A600)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="10" t="s">
         <v>37</v>
       </c>
       <c r="E1" s="8">
         <f>SUM(E3:E600)</f>
-        <v>1067.8699999999999</v>
+        <v>1208.9599999999998</v>
       </c>
       <c r="F1" s="5">
         <f>COUNTA(F3:F600)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G1" s="5">
         <f>COUNTA(G3:G600)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H1" s="5">
         <f>COUNTA(H3:H600)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I1" s="5">
         <f>COUNTIF(I3:I600,"sim")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J1" s="14" t="s">
         <v>43</v>
@@ -1191,6 +1203,38 @@
         <v>12</v>
       </c>
       <c r="J16" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="10">
+        <v>15</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="11">
+        <v>46151</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="1">
+        <v>141.09</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" s="4" t="s">
         <v>32</v>
       </c>
     </row>
